--- a/artfynd/A 31603-2022 artfynd.xlsx
+++ b/artfynd/A 31603-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 31603-2022 artfynd.xlsx
+++ b/artfynd/A 31603-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>86432188</v>
+        <v>86432043</v>
       </c>
       <c r="B2" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106061</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,24 +686,36 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223597</v>
+        <v>221101</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>Impatiens noli-tangere</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
@@ -719,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>381822.6533571209</v>
+        <v>381696</v>
       </c>
       <c r="R2" t="n">
-        <v>6637729.129697189</v>
+        <v>6637797</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,24 +759,9 @@
           <t>2020-06-21</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-06-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Riklig</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,7 +776,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Kanterna av källsprång med omgivande fuktig mark</t>
+          <t>örtrikt bäckdråg</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -802,15 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>86432043</v>
+        <v>86432188</v>
       </c>
       <c r="B3" t="n">
-        <v>103088</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99038</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -818,36 +805,24 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221101</v>
+        <v>223597</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -858,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>381695.9030381251</v>
+        <v>381823</v>
       </c>
       <c r="R3" t="n">
-        <v>6637796.505071976</v>
+        <v>6637729</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -891,19 +866,14 @@
           <t>2020-06-21</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-06-21</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Riklig</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,7 +888,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>örtrikt bäckdråg</t>
+          <t>Kanterna av källsprång med omgivande fuktig mark</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
